--- a/artfynd/S 9703-2021 artfynd.xlsx
+++ b/artfynd/S 9703-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712522</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712575</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712508</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,6 +1171,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712581</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712574</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1406,6 +1436,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712590</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1522,6 +1557,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129713283</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1638,6 +1678,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129713356</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1759,6 +1804,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486684</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1880,6 +1930,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486446</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2001,6 +2056,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486543</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2122,6 +2182,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486594</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2248,6 +2313,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486666</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2370,6 +2440,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486527</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2492,6 +2567,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486532</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2609,6 +2689,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712518</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2726,6 +2811,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712497</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2847,6 +2937,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486417</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2969,6 +3064,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486453</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3091,6 +3191,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486531</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3208,6 +3313,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712514</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3330,6 +3440,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486528</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3452,6 +3567,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486535</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3569,6 +3689,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712603</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3691,6 +3816,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486467</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3797,6 +3927,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486421</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3899,6 +4034,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712606</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4015,6 +4155,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129713360</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4128,6 +4273,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486469</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4253,6 +4403,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486424</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4379,6 +4534,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486438</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4480,6 +4640,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486443</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4606,6 +4771,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486533</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4732,6 +4902,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120486682</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4848,8 +5023,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129712579</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>